--- a/ExcelTools/Excel/ClipCfg.xlsx
+++ b/ExcelTools/Excel/ClipCfg.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28140" windowHeight="11660"/>
+    <workbookView windowWidth="27400" windowHeight="15540"/>
   </bookViews>
   <sheets>
     <sheet name="ClipCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>${name}</t>
   </si>
@@ -35,13 +35,22 @@
     <t>nClipID</t>
   </si>
   <si>
-    <t>strName</t>
+    <t>strDescEditor</t>
+  </si>
+  <si>
+    <t>bIsLoop</t>
   </si>
   <si>
     <t>fLength</t>
   </si>
   <si>
-    <t>nAssetCfgID</t>
+    <t>nLayer</t>
+  </si>
+  <si>
+    <t>nAssetID</t>
+  </si>
+  <si>
+    <t>bIsIK</t>
   </si>
   <si>
     <t>${desc}</t>
@@ -50,15 +59,24 @@
     <t>id</t>
   </si>
   <si>
-    <t>剪辑名字</t>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>是否循环</t>
   </si>
   <si>
     <t>长度</t>
   </si>
   <si>
+    <t>层级</t>
+  </si>
+  <si>
     <t>资源ID</t>
   </si>
   <si>
+    <t>是否启用脚部IK</t>
+  </si>
+  <si>
     <t>${type}</t>
   </si>
   <si>
@@ -77,7 +95,28 @@
     <t>c</t>
   </si>
   <si>
+    <t>e</t>
+  </si>
+  <si>
     <t>${key}</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>野蛮人静止</t>
+  </si>
+  <si>
+    <t>野蛮人攻击</t>
+  </si>
+  <si>
+    <t>野蛮人跑步</t>
+  </si>
+  <si>
+    <t>野蛮人死亡</t>
   </si>
 </sst>
 </file>
@@ -99,6 +138,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -110,7 +155,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -118,14 +163,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -141,7 +186,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -172,7 +217,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -180,7 +225,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -188,7 +233,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -196,14 +241,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -211,42 +256,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -555,154 +593,163 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1043,129 +1090,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="7"/>
   <cols>
-    <col min="5" max="5" width="12.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="37.3583333333333" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5">
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>111</v>
-      </c>
-      <c r="D6">
-        <v>2.33</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="2:5">
+      <c r="E6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>375</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7">
-        <v>111</v>
-      </c>
-      <c r="D7">
-        <v>2.33</v>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
       </c>
       <c r="E7">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1">
+        <v>370</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" customFormat="1" spans="2:5">
-      <c r="B8">
+      <c r="E8" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>378</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C8">
-        <v>111</v>
-      </c>
-      <c r="D8">
-        <v>2.33</v>
-      </c>
-      <c r="E8">
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1">
         <v>1</v>
       </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>373</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11" s="1"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13" s="1"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15" s="1"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16" s="1"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17" s="1"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2"/>
+      <c r="B18" s="1"/>
+      <c r="C18"/>
+      <c r="D18" s="1"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2"/>
+      <c r="B20" s="1"/>
+      <c r="C20"/>
+      <c r="D20" s="1"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21" s="1"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2"/>
+      <c r="B22" s="1"/>
+      <c r="C22"/>
+      <c r="D22" s="1"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23" s="1"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2"/>
+      <c r="B24" s="1"/>
+      <c r="C24"/>
+      <c r="D24" s="1"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2"/>
+      <c r="B26" s="1"/>
+      <c r="C26"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2"/>
+      <c r="B28" s="1"/>
+      <c r="C28"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31" s="1"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32" s="1"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33" s="1"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
